--- a/data/visc.xlsx
+++ b/data/visc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arkema-my.sharepoint.com/personal/a6131250_arkema_com/Documents/finish_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{8654C180-8CD7-4AD0-BC08-79CDDE6505BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78734EBC-8614-4028-9320-D88AF74BC344}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{8654C180-8CD7-4AD0-BC08-79CDDE6505BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92FD6630-EB34-445A-8150-A3889C82A5EB}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-15040" windowWidth="38620" windowHeight="21100" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-15040" windowWidth="38620" windowHeight="21100" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="up1_feed_0.25" sheetId="12" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="cond14" sheetId="11" r:id="rId11"/>
     <sheet name="cond15" sheetId="14" r:id="rId12"/>
     <sheet name="up1_up4_psd" sheetId="32" r:id="rId13"/>
+    <sheet name="sem_sample_no_filename" sheetId="33" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="solver_eng" localSheetId="11" hidden="1">1</definedName>
@@ -63,8 +64,116 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>LAI Christin</author>
+  </authors>
+  <commentList>
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{453FDF26-3A01-447F-8812-060F1AF6FBFA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>LAI Christin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+latex separate from bulk within minutes</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{7B305184-472D-449B-B04B-D878E89C2986}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>LAI Christin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+latex separate from bulk within minutes</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{381304EF-97CE-46EE-B64F-ACA87131774C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>LAI Christin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+data from 11:13:44
+latex does not separate from bulk immediately.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0" xr:uid="{EDAD04B2-C91D-4346-9CB5-CD2A8F74EE8A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>LAI Christin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+data from 11:13:44
+latex does not separate from bulk immediately.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="77">
   <si>
     <t>Sample 6</t>
   </si>
@@ -238,6 +347,63 @@
   </si>
   <si>
     <t>max_up4atom_psig</t>
+  </si>
+  <si>
+    <t>up4_Tin</t>
+  </si>
+  <si>
+    <t>up4_Tout</t>
+  </si>
+  <si>
+    <t>Sample No</t>
+  </si>
+  <si>
+    <t>Customer Ref</t>
+  </si>
+  <si>
+    <t>cond5</t>
+  </si>
+  <si>
+    <t>cond6</t>
+  </si>
+  <si>
+    <t>cond9</t>
+  </si>
+  <si>
+    <t>cond10</t>
+  </si>
+  <si>
+    <t>cond11</t>
+  </si>
+  <si>
+    <t>cond12</t>
+  </si>
+  <si>
+    <t>cond13</t>
+  </si>
+  <si>
+    <t>cond14</t>
+  </si>
+  <si>
+    <t>cond16</t>
+  </si>
+  <si>
+    <t>cond1</t>
+  </si>
+  <si>
+    <t>cond2</t>
+  </si>
+  <si>
+    <t>cond15</t>
+  </si>
+  <si>
+    <t>filename</t>
+  </si>
+  <si>
+    <t>SEM_X &lt;sample no&gt;_&lt;a/b/null&gt;&lt;magnification&gt;&lt;k/null&gt;x0</t>
+  </si>
+  <si>
+    <t>filename w/ k -&gt; &lt;magnification&gt; * 1000</t>
   </si>
 </sst>
 </file>
@@ -247,7 +413,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +443,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -311,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -341,6 +520,10 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="22" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1747,10 +1930,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE88FDC4-6F38-40E4-93A8-3A5E83D5592B}">
-  <dimension ref="B3:W21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE88FDC4-6F38-40E4-93A8-3A5E83D5592B}">
+  <dimension ref="A3:AE26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -1764,9 +1948,12 @@
     <col min="12" max="21" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>34</v>
       </c>
@@ -1833,8 +2020,17 @@
       <c r="W3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>44572.75</v>
+      </c>
       <c r="B4">
         <v>2</v>
       </c>
@@ -1901,8 +2097,18 @@
       <c r="W4">
         <v>4.6829000000000001</v>
       </c>
-    </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X4">
+        <v>152.33621215820313</v>
+      </c>
+      <c r="Y4">
+        <v>87.462631225585938</v>
+      </c>
+      <c r="AB4" s="15"/>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>44572.75</v>
+      </c>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1969,8 +2175,18 @@
       <c r="W5" s="7">
         <v>4.6829000000000001</v>
       </c>
-    </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X5">
+        <v>152.33621215820313</v>
+      </c>
+      <c r="Y5">
+        <v>87.462631225585938</v>
+      </c>
+      <c r="AB5" s="15"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>44574.560416666667</v>
+      </c>
       <c r="B6">
         <v>4</v>
       </c>
@@ -2037,8 +2253,18 @@
       <c r="W6">
         <v>4.1177999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X6">
+        <v>151.83699035644531</v>
+      </c>
+      <c r="Y6">
+        <v>87.915382385253906</v>
+      </c>
+      <c r="AB6" s="15"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
+        <v>44574.560416666667</v>
+      </c>
       <c r="B7" s="11">
         <v>4</v>
       </c>
@@ -2105,8 +2331,18 @@
       <c r="W7" s="11">
         <v>4.1177999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X7">
+        <v>151.83699035644531</v>
+      </c>
+      <c r="Y7">
+        <v>87.915382385253906</v>
+      </c>
+      <c r="AB7" s="15"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
+        <v>44582.472222222219</v>
+      </c>
       <c r="B8">
         <v>5</v>
       </c>
@@ -2173,8 +2409,18 @@
       <c r="W8">
         <v>5.9523999999999999</v>
       </c>
-    </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X8">
+        <v>151.85995483398438</v>
+      </c>
+      <c r="Y8">
+        <v>87.683334350585938</v>
+      </c>
+      <c r="AB8" s="15"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>44582.472222222219</v>
+      </c>
       <c r="B9" s="7">
         <v>5</v>
       </c>
@@ -2241,8 +2487,20 @@
       <c r="W9" s="7">
         <v>5.9523999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X9">
+        <v>151.85995483398438</v>
+      </c>
+      <c r="Y9">
+        <v>87.683334350585938</v>
+      </c>
+      <c r="AB9" s="15"/>
+      <c r="AD9" s="18"/>
+      <c r="AE9" s="18"/>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>44593.729166666664</v>
+      </c>
       <c r="B10">
         <v>8</v>
       </c>
@@ -2309,8 +2567,21 @@
       <c r="W10">
         <v>2.6657999999999999</v>
       </c>
-    </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X10">
+        <v>151.76530456542969</v>
+      </c>
+      <c r="Y10">
+        <v>87.718025207519531</v>
+      </c>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="18"/>
+      <c r="AD10" s="18"/>
+      <c r="AE10" s="18"/>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>44593.729166666664</v>
+      </c>
       <c r="B11">
         <v>8</v>
       </c>
@@ -2377,8 +2648,21 @@
       <c r="W11">
         <v>2.6657999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X11">
+        <v>151.76530456542969</v>
+      </c>
+      <c r="Y11">
+        <v>87.718025207519531</v>
+      </c>
+      <c r="AB11" s="15"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="18"/>
+      <c r="AE11" s="18"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
+        <v>44594.556944444441</v>
+      </c>
       <c r="B12">
         <v>9</v>
       </c>
@@ -2445,8 +2729,21 @@
       <c r="W12">
         <v>2.8338999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X12">
+        <v>152.52622985839844</v>
+      </c>
+      <c r="Y12">
+        <v>88.082786560058594</v>
+      </c>
+      <c r="AB12" s="15"/>
+      <c r="AC12" s="18"/>
+      <c r="AD12" s="18"/>
+      <c r="AE12" s="18"/>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>44594.556944444441</v>
+      </c>
       <c r="B13" s="7">
         <v>9</v>
       </c>
@@ -2513,8 +2810,20 @@
       <c r="W13" s="7">
         <v>2.8338999999999999</v>
       </c>
-    </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X13">
+        <v>152.52622985839844</v>
+      </c>
+      <c r="Y13">
+        <v>88.082786560058594</v>
+      </c>
+      <c r="AB13" s="15"/>
+      <c r="AD13" s="18"/>
+      <c r="AE13" s="18"/>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" s="15">
+        <v>44595.522916666669</v>
+      </c>
       <c r="B14">
         <v>11</v>
       </c>
@@ -2581,8 +2890,20 @@
       <c r="W14" s="12">
         <v>6.5354000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X14">
+        <v>153.54489135742188</v>
+      </c>
+      <c r="Y14">
+        <v>88.836555480957031</v>
+      </c>
+      <c r="AB14" s="15"/>
+      <c r="AD14" s="18"/>
+      <c r="AE14" s="18"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>44595.522916666669</v>
+      </c>
       <c r="B15" s="7">
         <v>11</v>
       </c>
@@ -2649,8 +2970,20 @@
       <c r="W15" s="13">
         <v>6.5354000000000001</v>
       </c>
-    </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X15">
+        <v>153.54489135742188</v>
+      </c>
+      <c r="Y15">
+        <v>88.836555480957031</v>
+      </c>
+      <c r="AB15" s="15"/>
+      <c r="AD15" s="18"/>
+      <c r="AE15" s="18"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
+        <v>44596.478472222225</v>
+      </c>
       <c r="B16">
         <v>12</v>
       </c>
@@ -2717,8 +3050,20 @@
       <c r="W16">
         <v>11.359</v>
       </c>
-    </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X16">
+        <v>152.75398254394531</v>
+      </c>
+      <c r="Y16">
+        <v>87.939712524414063</v>
+      </c>
+      <c r="AB16" s="15"/>
+      <c r="AD16" s="18"/>
+      <c r="AE16" s="18"/>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
+        <v>44596.478472222225</v>
+      </c>
       <c r="B17">
         <v>12</v>
       </c>
@@ -2785,8 +3130,20 @@
       <c r="W17">
         <v>11.359</v>
       </c>
-    </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X17">
+        <v>152.75398254394531</v>
+      </c>
+      <c r="Y17">
+        <v>87.939712524414063</v>
+      </c>
+      <c r="AB17" s="15"/>
+      <c r="AD17" s="18"/>
+      <c r="AE17" s="18"/>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18" s="15">
+        <v>44600.710416666669</v>
+      </c>
       <c r="B18">
         <v>14</v>
       </c>
@@ -2853,8 +3210,20 @@
       <c r="W18">
         <v>10.678000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X18">
+        <v>151.90849304199219</v>
+      </c>
+      <c r="Y18">
+        <v>87.595321655273438</v>
+      </c>
+      <c r="AB18" s="15"/>
+      <c r="AD18" s="18"/>
+      <c r="AE18" s="18"/>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>44600.710416666669</v>
+      </c>
       <c r="B19">
         <v>14</v>
       </c>
@@ -2921,8 +3290,20 @@
       <c r="W19">
         <v>10.678000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X19">
+        <v>151.90849304199219</v>
+      </c>
+      <c r="Y19">
+        <v>87.595321655273438</v>
+      </c>
+      <c r="AB19" s="15"/>
+      <c r="AD19" s="18"/>
+      <c r="AE19" s="18"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20" s="15">
+        <v>44601.651388888888</v>
+      </c>
       <c r="B20">
         <v>15</v>
       </c>
@@ -2989,8 +3370,20 @@
       <c r="W20">
         <v>9.9979999999999993</v>
       </c>
-    </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X20">
+        <v>151.6046142578125</v>
+      </c>
+      <c r="Y20">
+        <v>88.831771850585938</v>
+      </c>
+      <c r="AB20" s="15"/>
+      <c r="AD20" s="18"/>
+      <c r="AE20" s="18"/>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <v>44601.651388888888</v>
+      </c>
       <c r="B21" s="11">
         <v>15</v>
       </c>
@@ -3056,6 +3449,165 @@
       </c>
       <c r="W21" s="11">
         <v>9.9979999999999993</v>
+      </c>
+      <c r="X21">
+        <v>151.6046142578125</v>
+      </c>
+      <c r="Y21">
+        <v>88.831771850585938</v>
+      </c>
+      <c r="AB21" s="15"/>
+      <c r="AD21" s="18"/>
+      <c r="AE21" s="18"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AD22" s="18"/>
+      <c r="AE22" s="18"/>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AD23" s="18"/>
+      <c r="AE23" s="18"/>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AD24" s="18"/>
+      <c r="AE24" s="18"/>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AD25" s="18"/>
+      <c r="AE25" s="18"/>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AD26" s="18"/>
+      <c r="AE26" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80B6733-FA0A-4717-9B3B-0C866917780A}">
+  <dimension ref="B3:D15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>110041</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>110042</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>110043</v>
+      </c>
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>110044</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>110045</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>110046</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>110047</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>110048</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>110049</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>110494</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>110495</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>109384</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -5240,6 +5792,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F68CCE2449B7B14CB61E41C2B2490B10" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cc3e0e83755b6c5b39e5e5b4b56bcda6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="957b4867-70ba-4cfc-af85-fa94f3735f3b" xmlns:ns4="42e40f89-9189-4e16-8e72-5c7631d8a301" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f1591627019b8836b15c8cad4affd2d6" ns3:_="" ns4:_="">
     <xsd:import namespace="957b4867-70ba-4cfc-af85-fa94f3735f3b"/>
@@ -5468,15 +6029,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -5492,6 +6044,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC926051-3D1D-417D-9DE4-ADB150B0A389}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51044205-3C5D-49D4-B25A-DFC13F8D6B65}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5506,14 +6066,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC926051-3D1D-417D-9DE4-ADB150B0A389}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5536,7 +6088,7 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44024889-E8F4-4F58-863A-A0B6720F1F77}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA70CE3F-3B1F-42F4-9C4A-F14142C5A1FA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.aspentech.com/ProcessData/ExcelAddIn/IP21ConfigWorkBook"/>
